--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107145</v>
+        <v>107146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107146</v>
+        <v>107147</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -708,6 +708,9 @@
           <t>5</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mossaryd, Sm</t>
@@ -763,14 +766,10 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Christine Sandberg</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -779,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Melina Eberhagen</t>
+          <t>Melina Eberhagen, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107147</v>
+        <v>107155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107155</v>
+        <v>107248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107248</v>
+        <v>107271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107271</v>
+        <v>107283</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107283</v>
+        <v>107292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107292</v>
+        <v>107297</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107297</v>
+        <v>107325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107325</v>
+        <v>107338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Melina Eberhagen, Christine Sandberg</t>
+          <t>Christine Sandberg, Melina Eberhagen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128201935</v>
       </c>
       <c r="B2" t="n">
-        <v>107338</v>
+        <v>107908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -778,7 +778,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Christine Sandberg, Melina Eberhagen</t>
+          <t>Melina Eberhagen, Christine Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 23370-2023 artfynd.xlsx
+++ b/artfynd/A 23370-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,8 +791,16 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128201935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>